--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_los_rios.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_los_rios.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>10.39</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>9.880000000000001</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>9.130000000000001</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>8.74</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>8.609999999999999</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>8.42</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>7.91</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>7.51</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>7.04</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>6.94</v>
       </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>5.38</v>
       </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -538,9 +500,6 @@
       </c>
       <c r="B13">
         <v>4.74</v>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_los_rios.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_los_rios.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>10.39</v>
       </c>
+      <c r="C2">
+        <v>10.14</v>
+      </c>
+      <c r="D2">
+        <v>0.25</v>
+      </c>
+      <c r="E2">
+        <v>2.465483234714005</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>9.880000000000001</v>
       </c>
+      <c r="C3">
+        <v>10.29</v>
+      </c>
+      <c r="D3">
+        <v>-0.4099999999999984</v>
+      </c>
+      <c r="E3">
+        <v>-3.984450923226412</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>9.130000000000001</v>
       </c>
+      <c r="C4">
+        <v>9.43</v>
+      </c>
+      <c r="D4">
+        <v>-0.2999999999999989</v>
+      </c>
+      <c r="E4">
+        <v>-3.181336161187687</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,6 +448,15 @@
       <c r="B5">
         <v>8.74</v>
       </c>
+      <c r="C5">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="D5">
+        <v>0.3599999999999994</v>
+      </c>
+      <c r="E5">
+        <v>4.295942720763724</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -441,6 +477,15 @@
       <c r="B7">
         <v>8.42</v>
       </c>
+      <c r="C7">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="D7">
+        <v>-0.04000000000000092</v>
+      </c>
+      <c r="E7">
+        <v>-0.4728132387706974</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -451,6 +496,15 @@
       <c r="B8">
         <v>7.91</v>
       </c>
+      <c r="C8">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="D8">
+        <v>-0.3699999999999992</v>
+      </c>
+      <c r="E8">
+        <v>-4.468599033816412</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -461,6 +515,15 @@
       <c r="B9">
         <v>7.51</v>
       </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+      <c r="D9">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E9">
+        <v>0.1333333333333409</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -471,6 +534,15 @@
       <c r="B10">
         <v>7.04</v>
       </c>
+      <c r="C10">
+        <v>6.46</v>
+      </c>
+      <c r="D10">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="E10">
+        <v>8.978328173374607</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -481,25 +553,71 @@
       <c r="B11">
         <v>6.94</v>
       </c>
+      <c r="C11">
+        <v>6.82</v>
+      </c>
+      <c r="D11">
+        <v>0.1200000000000001</v>
+      </c>
+      <c r="E11">
+        <v>1.759530791788855</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Valdivia</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B12">
-        <v>5.38</v>
+        <v>6.89</v>
+      </c>
+      <c r="C12">
+        <v>6.76</v>
+      </c>
+      <c r="D12">
+        <v>0.1299999999999999</v>
+      </c>
+      <c r="E12">
+        <v>1.923076923076916</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>5.38</v>
+      </c>
+      <c r="C13">
+        <v>5.25</v>
+      </c>
+      <c r="D13">
+        <v>0.1299999999999999</v>
+      </c>
+      <c r="E13">
+        <v>2.476190476190476</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Corral</t>
         </is>
       </c>
-      <c r="B13">
+      <c r="B14">
         <v>4.74</v>
+      </c>
+      <c r="C14">
+        <v>4.59</v>
+      </c>
+      <c r="D14">
+        <v>0.1500000000000004</v>
+      </c>
+      <c r="E14">
+        <v>3.267973856209161</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_los_rios.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_los_rios.xlsx
@@ -627,7 +627,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -636,50 +636,33 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Corral</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>4.74</v>
+          <t>La Unión</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Futrono</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>10.39</v>
+          <t>Los Lagos</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>La Unión</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>7.91</v>
+          <t>Máfil</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lago Ranco</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>9.130000000000001</v>
+          <t>Paillaco</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -688,28 +671,19 @@
           <t>Lanco</t>
         </is>
       </c>
-      <c r="B6">
-        <v>6.94</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>8.42</v>
+          <t>Panguipulli</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Máfil</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>7.51</v>
+          <t>Río Bueno</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -718,48 +692,33 @@
           <t>Mariquina</t>
         </is>
       </c>
-      <c r="B9">
-        <v>7.04</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paillaco</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>9.880000000000001</v>
+          <t>Corral</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>8.74</v>
+          <t>Valdivia</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Río Bueno</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>8.609999999999999</v>
+          <t>Lago Ranco</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>5.38</v>
+          <t>Futrono</t>
+        </is>
       </c>
     </row>
   </sheetData>
